--- a/frontend/public/uhpc_import_template.xlsx
+++ b/frontend/public/uhpc_import_template.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\水泥配比\资料\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C8CB547-C90B-4FAF-98F3-5D26D205BEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="配比导入模板" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <r>
       <rPr>
@@ -51,7 +45,7 @@
         <sz val="18"/>
         <color rgb="FF1F4E79"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> · </t>
     </r>
@@ -83,6 +77,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
       <t>C130</t>
     </r>
     <r>
@@ -124,7 +124,7 @@
         <sz val="12"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>/MPa</t>
     </r>
@@ -146,16 +146,19 @@
         <sz val="12"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>/mm</t>
     </r>
   </si>
   <si>
-    <t>抗拉强度/MPa</t>
+    <t>抗拉强度等级/MPa</t>
   </si>
   <si>
     <t>其他</t>
+  </si>
+  <si>
+    <t>UT05</t>
   </si>
   <si>
     <t>三、原材料性能</t>
@@ -177,7 +180,7 @@
         <sz val="12"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>/kg/m³</t>
     </r>
@@ -229,7 +232,7 @@
         <sz val="12"/>
         <color theme="0"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> W/B</t>
     </r>
@@ -251,7 +254,7 @@
         <sz val="12"/>
         <color theme="0"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>/%</t>
     </r>
@@ -273,7 +276,7 @@
         <sz val="12"/>
         <color theme="0"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>/%</t>
     </r>
@@ -295,7 +298,7 @@
         <sz val="12"/>
         <color theme="0"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>/%</t>
     </r>
@@ -317,7 +320,7 @@
         <sz val="12"/>
         <color theme="0"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>/%</t>
     </r>
@@ -348,7 +351,7 @@
         <sz val="12"/>
         <color theme="0"/>
         <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <charset val="134"/>
       </rPr>
       <t>/%</t>
     </r>
@@ -373,17 +376,301 @@
   </si>
   <si>
     <t>每方用量(kg/m3)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>注：</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）绿色方框需输入数值，黄色方框为计算值，无需输入；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）配合比类型：高性能混凝土为</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>HPC</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；超高性能混凝土为</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>UHPC</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）抗拉强度等级，填写</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>UT05</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>UT07</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）扩展度和抗拉强度填写具体数值或范围的平均值，不写范围；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）各原材料表观密度有实测值时填写实测值；无实测值可参考软件中的推荐值；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+6</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）粒径对应的三个参数宜采用实测值；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）实验室配合比第三行为试拌体积下的用量，填写试拌体积，单位为</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）不涉及的方框，不用填写任何内容，空着即可。</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,7 +682,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -408,7 +695,7 @@
       <sz val="18"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -422,7 +709,7 @@
       <sz val="14"/>
       <color rgb="FF1F4E79"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -436,18 +723,18 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -484,33 +771,184 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -541,8 +979,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -602,16 +1226,349 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -648,66 +1605,83 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -992,454 +1966,611 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF4472C4"/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6333333333333" style="1" customWidth="1"/>
     <col min="2" max="8" width="12" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.8833333333333" style="1" customWidth="1"/>
     <col min="10" max="11" width="12" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+    <row r="1" ht="24.75" spans="1:11">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-    </row>
-    <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+    </row>
+    <row r="2" ht="21" spans="1:11">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="18"/>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" ht="18" spans="1:11">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="20" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="22"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="20" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="20" t="s">
+      <c r="H3" s="8"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="23"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" ht="15.75" spans="1:11">
+      <c r="A4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="26" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="26" t="s">
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="26" t="s">
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="28"/>
-    </row>
-    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="K4" s="12"/>
+    </row>
+    <row r="5" ht="21" spans="1:11">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="18"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" ht="18" spans="1:11">
+      <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="22"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="20" t="s">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="22"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="20" t="s">
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="20" t="s">
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="23"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="24">
-        <v>130</v>
-      </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="26">
+      <c r="K6" s="9"/>
+    </row>
+    <row r="7" ht="15.75" spans="1:11">
+      <c r="A7" s="13">
+        <v>150</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="10">
         <v>650</v>
       </c>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="26">
-        <v>5</v>
-      </c>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="28"/>
-    </row>
-    <row r="8" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="18"/>
-    </row>
-    <row r="9" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="12"/>
+    </row>
+    <row r="8" ht="21" spans="1:11">
+      <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" ht="18" spans="1:11">
+      <c r="A9" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-    </row>
-    <row r="10" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+    </row>
+    <row r="10" ht="18" spans="1:11">
+      <c r="A10" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="B10" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="C10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="D10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="E10" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="21"/>
-      <c r="H10" s="20" t="s">
+      <c r="F10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="21"/>
-      <c r="J10" s="20" t="s">
+      <c r="G10" s="16"/>
+      <c r="H10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="K10" s="21"/>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+      <c r="I10" s="16"/>
+      <c r="J10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="16"/>
+    </row>
+    <row r="11" ht="15.75" spans="1:11">
+      <c r="A11" s="17">
         <v>3100</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="17">
         <v>2200</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="17">
         <v>2100</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="17">
         <v>2400</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="17">
         <v>2650</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="18">
         <v>80</v>
       </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15">
+      <c r="G11" s="18"/>
+      <c r="H11" s="18">
         <v>18</v>
       </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15">
+      <c r="I11" s="18"/>
+      <c r="J11" s="18">
         <v>4</v>
       </c>
-      <c r="K11" s="15"/>
-    </row>
-    <row r="12" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="18"/>
-    </row>
-    <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="K11" s="18"/>
+    </row>
+    <row r="12" ht="21" spans="1:11">
+      <c r="A12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" ht="18" spans="1:11">
+      <c r="A13" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="B13" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="C13" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="E13" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="F13" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="G13" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="H13" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="I13" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+    </row>
+    <row r="14" ht="15.75" spans="1:11">
+      <c r="A14" s="21">
         <f>H17/F14</f>
-        <v>0.17</v>
-      </c>
-      <c r="B14" s="8">
+        <v>0.16</v>
+      </c>
+      <c r="B14" s="22">
         <f>B17/$F$14*100</f>
         <v>70</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="22">
         <f>C17/$F$14*100</f>
         <v>10</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="22">
         <f>D17/$F$14*100</f>
         <v>10</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="22">
         <f>E17/$F$14*100</f>
         <v>10</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="23">
         <f>B17+C17+D17+E17</f>
         <v>1000</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="23">
         <f>G17/78.5</f>
         <v>2</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="21">
         <f>F17/F14</f>
         <v>1.2</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="21">
         <f>I17/F14*100</f>
         <v>2.5</v>
       </c>
-      <c r="J14" s="10"/>
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="18"/>
-    </row>
-    <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="J14" s="24"/>
+      <c r="K14" s="18"/>
+    </row>
+    <row r="15" ht="21" spans="1:11">
+      <c r="A15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" ht="18" spans="1:11">
+      <c r="A16" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="C16" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="D16" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="E16" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="F16" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="H16" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2" t="s">
+      <c r="I16" s="15" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="J16" s="15"/>
+      <c r="K16" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="3">
+    </row>
+    <row r="17" ht="15.75" spans="1:11">
+      <c r="A17" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="17">
         <v>700</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="17">
         <v>100</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="17">
         <v>100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="17">
         <v>100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="17">
         <v>1200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="17">
         <v>157</v>
       </c>
-      <c r="H17" s="3">
-        <v>170</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="H17" s="17">
+        <v>160</v>
+      </c>
+      <c r="I17" s="17">
         <v>25</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="13">
+      <c r="J17" s="17"/>
+      <c r="K17" s="27">
         <f>SUM(B17:J17)</f>
-        <v>2552</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:11">
+      <c r="A18" s="28">
         <v>20</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="27">
         <f>B17*$A$18/1000</f>
         <v>14</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="27">
         <f t="shared" ref="C18:K18" si="0">C17*$A$18/1000</f>
         <v>2</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="27">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="27">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="27">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="27">
         <f t="shared" si="0"/>
         <v>3.14</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="27">
         <f t="shared" si="0"/>
-        <v>3.4</v>
-      </c>
-      <c r="I18" s="13">
+        <v>3.2</v>
+      </c>
+      <c r="I18" s="27">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13">
+      <c r="J18" s="27"/>
+      <c r="K18" s="27">
         <f t="shared" si="0"/>
-        <v>51.04</v>
-      </c>
+        <v>50.84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="31"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="33"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="32"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="33"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="32"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="33"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="32"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="33"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="32"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="33"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="32"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="33"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="32"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="33"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="32"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="33"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="32"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="33"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="32"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="33"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="34"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
+      <c r="K30" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:C3"/>
@@ -1470,8 +2601,9 @@
     <mergeCell ref="J11:K11"/>
     <mergeCell ref="A12:K12"/>
     <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A19:K30"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>